--- a/data/raw/sales/Week 35/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 35/Audio_Array/other_channels.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2B" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blinkit Sales" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D2C - Audio Array" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flipkart" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1387,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,6 +1619,136 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79958</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AM-W24</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA75673</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AM-C1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6425.42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA75691</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0B4G5JG4P</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AM-W14</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4772.88</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
